--- a/data/trans_bre/P37-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P37-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 1,03</t>
+          <t>-3,53; 1,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 0,22</t>
+          <t>-5,89; 0,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,47</t>
+          <t>-4,32; 1,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 15,16</t>
+          <t>2,86; 14,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-71,23; 45,73</t>
+          <t>-72,57; 52,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-73,2; 7,14</t>
+          <t>-74,37; 6,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-63,09; 51,1</t>
+          <t>-63,43; 38,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23,61; 865,63</t>
+          <t>26,06; 921,44</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,5</t>
+          <t>-2,99; 1,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,89</t>
+          <t>-3,15; 2,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,51</t>
+          <t>-2,22; 2,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 8,8</t>
+          <t>-3,77; 9,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,32; 44,11</t>
+          <t>-55,01; 48,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,72; 38,2</t>
+          <t>-45,36; 42,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,17; 84,47</t>
+          <t>-43,25; 89,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 106,12</t>
+          <t>-25,05; 107,53</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,54</t>
+          <t>-1,83; 3,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 2,52</t>
+          <t>-3,03; 2,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,27</t>
+          <t>1,51; 6,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 4,47</t>
+          <t>-3,77; 4,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 79,22</t>
+          <t>-25,92; 89,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,31; 44,16</t>
+          <t>-35,37; 43,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,84; 350,86</t>
+          <t>36,26; 318,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 33,4</t>
+          <t>-20,38; 32,05</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 0,79</t>
+          <t>-5,4; 0,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 2,14</t>
+          <t>-4,5; 2,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 1,89</t>
+          <t>-4,4; 1,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 16,06</t>
+          <t>0,05; 16,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,17; 17,09</t>
+          <t>-59,29; 13,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,0; 31,97</t>
+          <t>-45,99; 38,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,53; 31,41</t>
+          <t>-44,23; 28,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 268,84</t>
+          <t>-0,66; 213,3</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 4,9</t>
+          <t>-6,07; 4,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 5,45</t>
+          <t>-5,91; 4,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 3,08</t>
+          <t>-7,13; 3,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 4,61</t>
+          <t>-4,63; 4,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,62; 32,51</t>
+          <t>-27,94; 25,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 32,28</t>
+          <t>-26,45; 26,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,83; 19,41</t>
+          <t>-32,98; 20,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 13,48</t>
+          <t>-11,88; 14,2</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 12,51</t>
+          <t>-3,1; 11,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,56; -0,89</t>
+          <t>-17,44; -2,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 4,26</t>
+          <t>-11,77; 3,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 22,63</t>
+          <t>-1,63; 19,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 35,22</t>
+          <t>-7,03; 33,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,36; -1,85</t>
+          <t>-28,72; -4,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 10,32</t>
+          <t>-23,17; 7,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 32,72</t>
+          <t>-2,06; 28,37</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 1,36</t>
+          <t>-14,87; 1,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 4,12</t>
+          <t>-11,46; 3,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 0,13</t>
+          <t>-14,22; 1,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 2,56</t>
+          <t>-5,25; 2,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 2,16</t>
+          <t>-20,49; 3,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 5,87</t>
+          <t>-15,88; 5,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 0,2</t>
+          <t>-20,48; 2,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 2,99</t>
+          <t>-5,8; 2,62</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,78</t>
+          <t>0,24; 3,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,44</t>
+          <t>-1,31; 2,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,46</t>
+          <t>-0,15; 3,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,57; 22,68</t>
+          <t>4,43; 20,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,02; 29,0</t>
+          <t>1,86; 29,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 14,79</t>
+          <t>-6,84; 15,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 23,56</t>
+          <t>-1,06; 23,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,35; 91,46</t>
+          <t>14,03; 79,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P37-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P37-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,79</t>
+          <t>8,64</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>232,65%</t>
+          <t>256,79%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,07</t>
+          <t>-3,63; 0,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 0,04</t>
+          <t>-5,75; 0,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 1,34</t>
+          <t>-4,64; 1,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,86; 14,87</t>
+          <t>3,29; 14,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-72,57; 52,75</t>
+          <t>-72,43; 44,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-74,37; 6,14</t>
+          <t>-73,74; 6,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-63,43; 38,87</t>
+          <t>-65,04; 45,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,06; 921,44</t>
+          <t>35,64; 933,87</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,43</t>
+          <t>5,1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>45,82%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,62</t>
+          <t>-3,12; 1,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 2,01</t>
+          <t>-3,39; 2,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,51</t>
+          <t>-2,09; 2,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 9,05</t>
+          <t>-0,46; 9,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,01; 48,79</t>
+          <t>-54,95; 48,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,36; 42,96</t>
+          <t>-44,77; 48,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,25; 89,87</t>
+          <t>-41,18; 80,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 107,53</t>
+          <t>-3,96; 114,53</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,66</t>
+          <t>-1,77; 3,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 2,57</t>
+          <t>-3,19; 2,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,12</t>
+          <t>1,55; 6,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,4</t>
+          <t>-3,05; 4,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,92; 89,98</t>
+          <t>-25,75; 88,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,37; 43,67</t>
+          <t>-35,63; 40,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,26; 318,85</t>
+          <t>35,33; 361,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 32,05</t>
+          <t>-17,4; 38,68</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,86</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 0,8</t>
+          <t>-5,34; 0,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 2,38</t>
+          <t>-4,48; 2,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 1,89</t>
+          <t>-4,13; 1,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 16,42</t>
+          <t>-1,76; 6,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,29; 13,35</t>
+          <t>-57,98; 18,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,99; 38,14</t>
+          <t>-44,43; 31,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-44,23; 28,72</t>
+          <t>-42,48; 27,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 213,3</t>
+          <t>-7,92; 32,88</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 4,2</t>
+          <t>-6,19; 4,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 4,65</t>
+          <t>-5,5; 4,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 3,15</t>
+          <t>-7,11; 3,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 4,79</t>
+          <t>-3,93; 5,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-27,94; 25,82</t>
+          <t>-29,13; 27,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,45; 26,95</t>
+          <t>-24,86; 31,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,98; 20,19</t>
+          <t>-33,34; 18,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 14,2</t>
+          <t>-10,14; 15,76</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,19</t>
+          <t>1,64</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 11,96</t>
+          <t>-3,38; 11,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,44; -2,26</t>
+          <t>-17,05; -1,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 3,24</t>
+          <t>-10,59; 3,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 19,97</t>
+          <t>-2,93; 6,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 33,22</t>
+          <t>-7,34; 32,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-28,72; -4,29</t>
+          <t>-27,77; -3,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 7,58</t>
+          <t>-21,3; 8,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 28,37</t>
+          <t>-3,91; 9,15</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,49</t>
+          <t>-1,34</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-1,69%</t>
+          <t>-1,53%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 1,89</t>
+          <t>-14,26; 2,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 3,39</t>
+          <t>-11,46; 4,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 1,36</t>
+          <t>-14,23; 0,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 2,24</t>
+          <t>-5,45; 2,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 3,0</t>
+          <t>-20,19; 3,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 5,32</t>
+          <t>-15,91; 6,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 2,27</t>
+          <t>-20,44; 0,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 2,62</t>
+          <t>-6,04; 2,93</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10,04</t>
+          <t>5,07</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,72</t>
+          <t>0,26; 3,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,48</t>
+          <t>-1,34; 2,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 3,48</t>
+          <t>-0,33; 3,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,43; 20,9</t>
+          <t>2,8; 7,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,86; 29,17</t>
+          <t>1,67; 28,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 15,07</t>
+          <t>-7,15; 15,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 23,6</t>
+          <t>-1,99; 23,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,03; 79,88</t>
+          <t>8,78; 24,14</t>
         </is>
       </c>
     </row>
